--- a/assets/xlsx/투자수익현황_2026-08-01_2026-08-26.xlsx
+++ b/assets/xlsx/투자수익현황_2026-08-01_2026-08-26.xlsx
@@ -520,7 +520,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>연환산수익률 (투자실행금액 대비)</t>
+          <t>연환산 수익률 (투자실행금액 대비)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -530,7 +530,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>연환산수익률 (투자자산 대비)</t>
+          <t>연환산 수익률 (투자 자산 대비)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
